--- a/data/trending_integrated_20261028_15.xlsx
+++ b/data/trending_integrated_20261028_15.xlsx
@@ -578,13 +578,13 @@
         <v>-0.19</v>
       </c>
       <c r="E2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G2" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>151423346271</v>
+        <v>151452212066</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19760</v>
+        <v>19440</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+24.83%</t>
+          <t>'+22.80%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.02</v>
       </c>
       <c r="E3" t="n">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="F3" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G3" t="n">
-        <v>460</v>
+        <v>491</v>
       </c>
       <c r="H3" t="n">
         <v>1.11</v>
@@ -702,7 +702,7 @@
         <v>0.09</v>
       </c>
       <c r="O3" t="n">
-        <v>396711730655</v>
+        <v>408267213375</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 마이크론과의 협력 및 ASML 공급망 진입 관련 뉴스. 반도체 장비 공급 기대감.</t>
+          <t>미국 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 뉴스. 4분기 공급 가시화.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['마이크론', 'ASML', '공급망']</t>
+          <t>['반도체장비', '공급망', 'ASML']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27850</v>
+        <v>27900</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.26%</t>
+          <t>'+17.47%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -794,7 +794,7 @@
         <v>5.31</v>
       </c>
       <c r="O4" t="n">
-        <v>177318020425</v>
+        <v>178438549925</v>
       </c>
       <c r="P4" t="n">
         <v>50600</v>
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1489000</v>
+        <v>190300</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.04%</t>
+          <t>'+11.22%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>800</v>
+        <v>95</v>
       </c>
       <c r="F5" t="n">
-        <v>494</v>
+        <v>72</v>
       </c>
       <c r="G5" t="n">
-        <v>1965</v>
+        <v>467</v>
       </c>
       <c r="H5" t="n">
-        <v>48.61</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,91 +871,91 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1341000</v>
+        <v>171100</v>
       </c>
       <c r="K5" t="n">
-        <v>1390000</v>
+        <v>176300</v>
       </c>
       <c r="L5" t="n">
-        <v>1492000</v>
+        <v>190800</v>
       </c>
       <c r="M5" t="n">
-        <v>1358000</v>
+        <v>175400</v>
       </c>
       <c r="N5" t="n">
-        <v>48.66</v>
+        <v>74.89</v>
       </c>
       <c r="O5" t="n">
-        <v>4900391111500</v>
+        <v>774305157800</v>
       </c>
       <c r="P5" t="n">
-        <v>2987000</v>
+        <v>243500</v>
       </c>
       <c r="Q5" t="n">
-        <v>501000</v>
+        <v>71000</v>
       </c>
       <c r="R5" t="n">
-        <v>285000</v>
+        <v>1017000</v>
       </c>
       <c r="S5" t="n">
-        <v>211000</v>
+        <v>-28000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>반도체 업황 개선 및 실적 발표 이후 주가 상승 기대감. 목표가 상향 제시.</t>
+          <t>우선주 소각 및 실적 발표에 대한 기대감과 외국인 수급 긍정적. 숏 스퀴즈 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체 업황', '실적 발표', '목표가']</t>
+          <t>['우선주 소각', '실적 발표', '외국인 수급']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>189500</v>
+        <v>1491000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.75%</t>
+          <t>'+11.19%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>96</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>73</v>
+        <v>494</v>
       </c>
       <c r="G6" t="n">
-        <v>454</v>
+        <v>1949</v>
       </c>
       <c r="H6" t="n">
-        <v>74.90000000000001</v>
+        <v>48.61</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,60 +963,60 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>171100</v>
+        <v>1341000</v>
       </c>
       <c r="K6" t="n">
-        <v>176300</v>
+        <v>1390000</v>
       </c>
       <c r="L6" t="n">
-        <v>190800</v>
+        <v>1492000</v>
       </c>
       <c r="M6" t="n">
-        <v>175400</v>
+        <v>1358000</v>
       </c>
       <c r="N6" t="n">
-        <v>74.89</v>
+        <v>48.66</v>
       </c>
       <c r="O6" t="n">
-        <v>755421191400</v>
+        <v>5026346296000</v>
       </c>
       <c r="P6" t="n">
-        <v>243500</v>
+        <v>2987000</v>
       </c>
       <c r="Q6" t="n">
-        <v>71000</v>
+        <v>501000</v>
       </c>
       <c r="R6" t="n">
-        <v>1017000</v>
+        <v>285000</v>
       </c>
       <c r="S6" t="n">
-        <v>-28000</v>
+        <v>211000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>우선주 소각 및 실적 발표에 대한 기대감과 외국인 수급 긍정적. 숏 스퀴즈 가능성 언급.</t>
+          <t>연말 목표가 200~320만원 제시. 외국인 매수 시 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['우선주 소각', '실적 발표', '외국인 수급']</t>
+          <t>['목표가', '외국인', '주가상승']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14960</v>
+        <v>14940</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.20%</t>
+          <t>'+9.05%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F7" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G7" t="n">
-        <v>744</v>
+        <v>764</v>
       </c>
       <c r="H7" t="n">
         <v>2.87</v>
@@ -1070,7 +1070,7 @@
         <v>2.82</v>
       </c>
       <c r="O7" t="n">
-        <v>174068096280</v>
+        <v>175648037325</v>
       </c>
       <c r="P7" t="n">
         <v>31500</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>241500</v>
+        <v>241750</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.78%</t>
+          <t>'+8.90%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="G8" t="n">
-        <v>1640</v>
+        <v>1604</v>
       </c>
       <c r="H8" t="n">
         <v>46.15</v>
@@ -1162,7 +1162,7 @@
         <v>46.1</v>
       </c>
       <c r="O8" t="n">
-        <v>3422749043000</v>
+        <v>3517493321250</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>자사주 소각 및 주주환원 정책 발표 기대감 속 단기 급등 전망. 3분기 순이익 예상치 비교.</t>
+          <t>주주환원 110조 발표 기대감 속 폭등 전망. 3분기 예상 순이익 호조.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['자사주 소각', '주주환원', '순이익']</t>
+          <t>['주주환원', '순이익', '폭등']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19310</v>
+        <v>19270</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+7.94%</t>
+          <t>'+7.71%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.46</v>
       </c>
       <c r="E9" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H9" t="n">
         <v>4.25</v>
@@ -1254,7 +1254,7 @@
         <v>3.79</v>
       </c>
       <c r="O9" t="n">
-        <v>71803714045</v>
+        <v>72327948885</v>
       </c>
       <c r="P9" t="n">
         <v>22450</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18390</v>
+        <v>18400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+7.61%</t>
+          <t>'+7.67%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.61</v>
       </c>
       <c r="E10" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F10" t="n">
         <v>76</v>
       </c>
       <c r="G10" t="n">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="H10" t="n">
         <v>4.74</v>
@@ -1346,7 +1346,7 @@
         <v>4.13</v>
       </c>
       <c r="O10" t="n">
-        <v>46877527005</v>
+        <v>47138052120</v>
       </c>
       <c r="P10" t="n">
         <v>28600</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>로봇 및 AI 관련 사업 성장성 부각. 휴머노이드, 데이터센터 방열 시스템 등 신규 계약 수주 기대.</t>
+          <t>AI 데이터센터 방열 시스템 공급 계약 체결. 휴머노이드 및 로봇 관련주로 부각.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['로봇', 'AI', '휴머노이드']</t>
+          <t>['AI', '로봇', '공급계약']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9210</v>
+        <v>9180</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+6.72%</t>
+          <t>'+6.37%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.13</v>
       </c>
       <c r="E11" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F11" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G11" t="n">
-        <v>352</v>
+        <v>389</v>
       </c>
       <c r="H11" t="n">
         <v>5.47</v>
@@ -1438,7 +1438,7 @@
         <v>5.34</v>
       </c>
       <c r="O11" t="n">
-        <v>26647462770</v>
+        <v>27312111435</v>
       </c>
       <c r="P11" t="n">
         <v>14940</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>테슬라 관련 사업 진출 및 상표 출원 소식으로 인한 주가 상승 기대. 공매도 세력과의 경쟁.</t>
+          <t>테슬라 관련주로 부각되며 9천원대 돌파 기대. 공매도 세력과의 움직임 주목.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['테슬라', '상표 출원', '공매도']</t>
+          <t>['테슬라', '공매도', '상표출원']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8650</v>
+        <v>8710</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+5.49%</t>
+          <t>'+6.22%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1530,7 +1530,7 @@
         <v>1.15</v>
       </c>
       <c r="O12" t="n">
-        <v>126153643430</v>
+        <v>126766587795</v>
       </c>
       <c r="P12" t="n">
         <v>9820</v>
@@ -1579,21 +1579,21 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2570</v>
+        <v>2562</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+4.90%</t>
+          <t>'+4.57%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.68</v>
       </c>
       <c r="E13" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F13" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G13" t="n">
         <v>169</v>
@@ -1622,7 +1622,7 @@
         <v>1.01</v>
       </c>
       <c r="O13" t="n">
-        <v>89219744477</v>
+        <v>90147398505</v>
       </c>
       <c r="P13" t="n">
         <v>2965</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>64000</v>
+        <v>64200</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.89%</t>
+          <t>'+3.22%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.57</v>
       </c>
       <c r="E14" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F14" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G14" t="n">
-        <v>841</v>
+        <v>859</v>
       </c>
       <c r="H14" t="n">
         <v>41.01</v>
@@ -1714,7 +1714,7 @@
         <v>40.44</v>
       </c>
       <c r="O14" t="n">
-        <v>237421781550</v>
+        <v>241867979050</v>
       </c>
       <c r="P14" t="n">
         <v>67300</v>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>178300</v>
+        <v>178400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.29%</t>
+          <t>'+2.35%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="G15" t="n">
-        <v>2454</v>
+        <v>2392</v>
       </c>
       <c r="H15" t="n">
         <v>35.43</v>
@@ -1806,7 +1806,7 @@
         <v>35.49</v>
       </c>
       <c r="O15" t="n">
-        <v>178582403850</v>
+        <v>186207001750</v>
       </c>
       <c r="P15" t="n">
         <v>304000</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>타 종목 대비 저조한 주가 흐름에 대한 불만. 공매도 비율 및 외국인, 연기금 매도세 지적.</t>
+          <t>지수 대비 부진한 주가 흐름 및 공매도 비율 증가. 네이버 주가 반등 의지 부족.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공매도', '외국인 매도', '주가 부진']</t>
+          <t>['주가흐름', '공매도', '소외주']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>29900</v>
+        <v>29850</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.36%</t>
+          <t>'+1.19%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="F16" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G16" t="n">
-        <v>628</v>
+        <v>712</v>
       </c>
       <c r="H16" t="n">
         <v>28.81</v>
@@ -1892,13 +1892,13 @@
         <v>30650</v>
       </c>
       <c r="M16" t="n">
-        <v>29900</v>
+        <v>29850</v>
       </c>
       <c r="N16" t="n">
         <v>28.82</v>
       </c>
       <c r="O16" t="n">
-        <v>35492566625</v>
+        <v>36122122525</v>
       </c>
       <c r="P16" t="n">
         <v>69700</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주가 부진 및 전환사채 발행 관련 논란. 네이버 대비 경쟁력 약화 우려.</t>
+          <t>김범수 관련 이슈 지속되며 주가 약세. 전환사채 발행 및 유증 관련 의혹 제기.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['전환사채', '주가 부진', '경쟁력']</t>
+          <t>['김범수', '전환사채', '주가약세']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16480</v>
+        <v>16490</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.55%</t>
+          <t>'+0.61%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F17" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G17" t="n">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="H17" t="n">
         <v>28.03</v>
@@ -1990,7 +1990,7 @@
         <v>27.96</v>
       </c>
       <c r="O17" t="n">
-        <v>60035921120</v>
+        <v>61888959535</v>
       </c>
       <c r="P17" t="n">
         <v>35350</v>
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SK증권</t>
+          <t>한화오션</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2060</v>
+        <v>52400</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-1.20%</t>
+          <t>'-1.13%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.39</v>
+        <v>-0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>94</v>
+        <v>516</v>
       </c>
       <c r="F18" t="n">
-        <v>55</v>
+        <v>278</v>
       </c>
       <c r="G18" t="n">
-        <v>130</v>
+        <v>1423</v>
       </c>
       <c r="H18" t="n">
-        <v>2.52</v>
+        <v>10.31</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>2085</v>
+        <v>53000</v>
       </c>
       <c r="K18" t="n">
-        <v>2005</v>
+        <v>53400</v>
       </c>
       <c r="L18" t="n">
-        <v>2065</v>
+        <v>53800</v>
       </c>
       <c r="M18" t="n">
-        <v>1805</v>
+        <v>51200</v>
       </c>
       <c r="N18" t="n">
-        <v>2.13</v>
+        <v>10.34</v>
       </c>
       <c r="O18" t="n">
-        <v>16924177890</v>
+        <v>86088607450</v>
       </c>
       <c r="P18" t="n">
-        <v>6190</v>
+        <v>154800</v>
       </c>
       <c r="Q18" t="n">
-        <v>636</v>
+        <v>51200</v>
       </c>
       <c r="R18" t="n">
-        <v>-1288000</v>
+        <v>-412000</v>
       </c>
       <c r="S18" t="n">
-        <v>19000</v>
+        <v>-70000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>SK하이닉스 연계 호재 언급 있으나, 액면병합 및 공매도 관련 부정적 논조.</t>
+          <t>2분기 실적 호조에도 주가 하락 지속. 증권가 평가 및 미국 조선업 협력 난항 우려.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '공매도', '액면병합']</t>
+          <t>['실적', '주가하락', '조선업']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>001510</t>
+          <t>042660</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14270</v>
+        <v>14280</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-1.25%</t>
+          <t>'-1.18%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.19</v>
       </c>
       <c r="E19" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F19" t="n">
         <v>124</v>
       </c>
       <c r="G19" t="n">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="H19" t="n">
         <v>9.83</v>
@@ -2174,7 +2174,7 @@
         <v>10.02</v>
       </c>
       <c r="O19" t="n">
-        <v>66187181820</v>
+        <v>67257958205</v>
       </c>
       <c r="P19" t="n">
         <v>40350</v>
@@ -2219,31 +2219,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>SK증권</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>52300</v>
+        <v>2040</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-1.32%</t>
+          <t>'-2.16%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.03</v>
+        <v>0.39</v>
       </c>
       <c r="E20" t="n">
-        <v>505</v>
+        <v>96</v>
       </c>
       <c r="F20" t="n">
-        <v>275</v>
+        <v>55</v>
       </c>
       <c r="G20" t="n">
-        <v>1358</v>
+        <v>133</v>
       </c>
       <c r="H20" t="n">
-        <v>10.31</v>
+        <v>2.52</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,47 +2251,47 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>53000</v>
+        <v>2085</v>
       </c>
       <c r="K20" t="n">
-        <v>53400</v>
+        <v>2005</v>
       </c>
       <c r="L20" t="n">
-        <v>53800</v>
+        <v>2065</v>
       </c>
       <c r="M20" t="n">
-        <v>51200</v>
+        <v>1805</v>
       </c>
       <c r="N20" t="n">
-        <v>10.34</v>
+        <v>2.13</v>
       </c>
       <c r="O20" t="n">
-        <v>83451441450</v>
+        <v>17170029244</v>
       </c>
       <c r="P20" t="n">
-        <v>154800</v>
+        <v>6190</v>
       </c>
       <c r="Q20" t="n">
-        <v>51200</v>
+        <v>636</v>
       </c>
       <c r="R20" t="n">
-        <v>-412000</v>
+        <v>-1288000</v>
       </c>
       <c r="S20" t="n">
-        <v>-70000</v>
+        <v>19000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>대외 환경 악화 및 실적 부진으로 인한 주가 하락 지속. 투자자들의 실망감.</t>
+          <t>SK하이닉스 연계 호재 언급 있으나, 액면병합 및 공매도 관련 부정적 논조.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['실적 부진', '대외 악재', '주가 하락']</t>
+          <t>['SK하이닉스', '공매도', '액면병합']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>042660</t>
+          <t>001510</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2090</v>
+        <v>2080</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-3.69%</t>
+          <t>'-4.15%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.18</v>
       </c>
       <c r="E21" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F21" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G21" t="n">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="H21" t="n">
         <v>5.07</v>
@@ -2358,7 +2358,7 @@
         <v>4.89</v>
       </c>
       <c r="O21" t="n">
-        <v>52295203570</v>
+        <v>52619875485</v>
       </c>
       <c r="P21" t="n">
         <v>4980</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9030</v>
+        <v>9000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-5.25%</t>
+          <t>'-5.56%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.83</v>
       </c>
       <c r="E22" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F22" t="n">
         <v>56</v>
       </c>
       <c r="G22" t="n">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="H22" t="n">
         <v>3.46</v>
@@ -2450,7 +2450,7 @@
         <v>2.63</v>
       </c>
       <c r="O22" t="n">
-        <v>46400399095</v>
+        <v>46989764455</v>
       </c>
       <c r="P22" t="n">
         <v>11690</v>

--- a/data/trending_integrated_20261028_15.xlsx
+++ b/data/trending_integrated_20261028_15.xlsx
@@ -584,7 +584,7 @@
         <v>87</v>
       </c>
       <c r="G2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>151452212066</v>
+        <v>151495479296</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19440</v>
+        <v>19130</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.80%</t>
+          <t>'+20.85%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.02</v>
       </c>
       <c r="E3" t="n">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F3" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G3" t="n">
-        <v>491</v>
+        <v>517</v>
       </c>
       <c r="H3" t="n">
         <v>1.11</v>
@@ -702,7 +702,7 @@
         <v>0.09</v>
       </c>
       <c r="O3" t="n">
-        <v>408267213375</v>
+        <v>415208854275</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -751,21 +751,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27900</v>
+        <v>27950</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.47%</t>
+          <t>'+17.68%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
         <v>284</v>
@@ -794,7 +794,7 @@
         <v>5.31</v>
       </c>
       <c r="O4" t="n">
-        <v>178438549925</v>
+        <v>180000014025</v>
       </c>
       <c r="P4" t="n">
         <v>50600</v>
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>190300</v>
+        <v>1494000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.22%</t>
+          <t>'+11.41%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>95</v>
+        <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>72</v>
+        <v>493</v>
       </c>
       <c r="G5" t="n">
-        <v>467</v>
+        <v>2000</v>
       </c>
       <c r="H5" t="n">
-        <v>74.90000000000001</v>
+        <v>48.61</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,91 +871,91 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>171100</v>
+        <v>1341000</v>
       </c>
       <c r="K5" t="n">
-        <v>176300</v>
+        <v>1390000</v>
       </c>
       <c r="L5" t="n">
-        <v>190800</v>
+        <v>1495000</v>
       </c>
       <c r="M5" t="n">
-        <v>175400</v>
+        <v>1358000</v>
       </c>
       <c r="N5" t="n">
-        <v>74.89</v>
+        <v>48.66</v>
       </c>
       <c r="O5" t="n">
-        <v>774305157800</v>
+        <v>5134076303500</v>
       </c>
       <c r="P5" t="n">
-        <v>243500</v>
+        <v>2987000</v>
       </c>
       <c r="Q5" t="n">
-        <v>71000</v>
+        <v>501000</v>
       </c>
       <c r="R5" t="n">
-        <v>1017000</v>
+        <v>285000</v>
       </c>
       <c r="S5" t="n">
-        <v>-28000</v>
+        <v>211000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>우선주 소각 및 실적 발표에 대한 기대감과 외국인 수급 긍정적. 숏 스퀴즈 가능성 언급.</t>
+          <t>SK하이닉스, 200만원 및 470만원 목표가 제시와 함께 외국인 매수세 유입 기대. 29년 목표가 320만원 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['우선주 소각', '실적 발표', '외국인 수급']</t>
+          <t>['목표가', '외국인', '실적발표']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1491000</v>
+        <v>190100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.19%</t>
+          <t>'+11.10%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>95</v>
       </c>
       <c r="F6" t="n">
-        <v>494</v>
+        <v>72</v>
       </c>
       <c r="G6" t="n">
-        <v>1949</v>
+        <v>468</v>
       </c>
       <c r="H6" t="n">
-        <v>48.61</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,60 +963,60 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1341000</v>
+        <v>171100</v>
       </c>
       <c r="K6" t="n">
-        <v>1390000</v>
+        <v>176300</v>
       </c>
       <c r="L6" t="n">
-        <v>1492000</v>
+        <v>190800</v>
       </c>
       <c r="M6" t="n">
-        <v>1358000</v>
+        <v>175400</v>
       </c>
       <c r="N6" t="n">
-        <v>48.66</v>
+        <v>74.89</v>
       </c>
       <c r="O6" t="n">
-        <v>5026346296000</v>
+        <v>789192738250</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>243500</v>
       </c>
       <c r="Q6" t="n">
-        <v>501000</v>
+        <v>71000</v>
       </c>
       <c r="R6" t="n">
-        <v>285000</v>
+        <v>1017000</v>
       </c>
       <c r="S6" t="n">
-        <v>211000</v>
+        <v>-28000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>연말 목표가 200~320만원 제시. 외국인 매수 시 주가 상승 기대.</t>
+          <t>우선주 소각 및 실적 발표에 대한 기대감과 외국인 수급 긍정적. 숏 스퀴즈 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['목표가', '외국인', '주가상승']</t>
+          <t>['우선주 소각', '실적 발표', '외국인 수급']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14940</v>
+        <v>14960</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.05%</t>
+          <t>'+9.20%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F7" t="n">
         <v>87</v>
       </c>
       <c r="G7" t="n">
-        <v>764</v>
+        <v>781</v>
       </c>
       <c r="H7" t="n">
         <v>2.87</v>
@@ -1070,7 +1070,7 @@
         <v>2.82</v>
       </c>
       <c r="O7" t="n">
-        <v>175648037325</v>
+        <v>177120895735</v>
       </c>
       <c r="P7" t="n">
         <v>31500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>국민연금의 광통신 섹터 매수 및 AI 수요 증가 기대. 메타 유리기판, 해상광통신 케이블 등 신규 기술 성장성 언급.</t>
+          <t>대한광통신, AI 수요 증가 및 메타 유리기판, 해상광통신 케이블 등 신기술 기반 2만원 돌파 전망. 외인 프로그램 적극 매수 및 미국 수주 유지.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['AI 수요', '광통신', '메타']</t>
+          <t>['AI수요', '유리기판', '수주']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>241750</v>
+        <v>242250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.90%</t>
+          <t>'+9.12%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="G8" t="n">
-        <v>1604</v>
+        <v>1592</v>
       </c>
       <c r="H8" t="n">
         <v>46.15</v>
@@ -1162,7 +1162,7 @@
         <v>46.1</v>
       </c>
       <c r="O8" t="n">
-        <v>3517493321250</v>
+        <v>3597711000000</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>주주환원 110조 발표 기대감 속 폭등 전망. 3분기 예상 순이익 호조.</t>
+          <t>삼성전자, 주주환원 110조 발표 및 3분기 순이익 115조 예상 속 폭등 기대감. 공매도 세력에 대한 경고 및 긍정적 추세 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주주환원', '순이익', '폭등']</t>
+          <t>['주주환원', '순이익', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,123 +1207,123 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>18390</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>'+7.61%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E9" t="n">
+        <v>148</v>
+      </c>
+      <c r="F9" t="n">
+        <v>79</v>
+      </c>
+      <c r="G9" t="n">
+        <v>432</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>17090</v>
+      </c>
+      <c r="K9" t="n">
         <v>19270</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>'+7.71%</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E9" t="n">
-        <v>98</v>
-      </c>
-      <c r="F9" t="n">
-        <v>50</v>
-      </c>
-      <c r="G9" t="n">
-        <v>122</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>17890</v>
-      </c>
-      <c r="K9" t="n">
-        <v>18250</v>
-      </c>
       <c r="L9" t="n">
-        <v>20000</v>
+        <v>20450</v>
       </c>
       <c r="M9" t="n">
-        <v>17950</v>
+        <v>18070</v>
       </c>
       <c r="N9" t="n">
-        <v>3.79</v>
+        <v>4.13</v>
       </c>
       <c r="O9" t="n">
-        <v>72327948885</v>
+        <v>47357230065</v>
       </c>
       <c r="P9" t="n">
-        <v>22450</v>
+        <v>28600</v>
       </c>
       <c r="Q9" t="n">
-        <v>6320</v>
+        <v>11050</v>
       </c>
       <c r="R9" t="n">
-        <v>-7000</v>
+        <v>-59000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>58000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>국내외 해킹 사고 연이은 발생, 양자보안 의무화 등 보안 섹터 상승 기대.</t>
+          <t>나무가, 11월 6일 로봇 눈 공개 및 AI 데이터센터 방열 시스템 594억 공급 계약 체결. 휴머노이드 및 현대차 로봇 2만 5천대 도입 관련 긍정적 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['보안', '해킹', '양자보안']</t>
+          <t>['로봇', '공급계약', '휴머노이드']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>190510</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18400</v>
+        <v>19250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+7.67%</t>
+          <t>'+7.60%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.61</v>
+        <v>0.46</v>
       </c>
       <c r="E10" t="n">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>420</v>
+        <v>123</v>
       </c>
       <c r="H10" t="n">
-        <v>4.74</v>
+        <v>4.25</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,60 +1331,60 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17090</v>
+        <v>17890</v>
       </c>
       <c r="K10" t="n">
-        <v>19270</v>
+        <v>18250</v>
       </c>
       <c r="L10" t="n">
-        <v>20450</v>
+        <v>20000</v>
       </c>
       <c r="M10" t="n">
-        <v>18070</v>
+        <v>17950</v>
       </c>
       <c r="N10" t="n">
-        <v>4.13</v>
+        <v>3.79</v>
       </c>
       <c r="O10" t="n">
-        <v>47138052120</v>
+        <v>72698052300</v>
       </c>
       <c r="P10" t="n">
-        <v>28600</v>
+        <v>22450</v>
       </c>
       <c r="Q10" t="n">
-        <v>11050</v>
+        <v>6320</v>
       </c>
       <c r="R10" t="n">
-        <v>-59000</v>
+        <v>-7000</v>
       </c>
       <c r="S10" t="n">
-        <v>58000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>AI 데이터센터 방열 시스템 공급 계약 체결. 휴머노이드 및 로봇 관련주로 부각.</t>
+          <t>국내외 해킹 사고 연이은 발생, 양자보안 의무화 등 보안 섹터 상승 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['AI', '로봇', '공급계약']</t>
+          <t>['보안', '해킹', '양자보안']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>190510</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9180</v>
+        <v>9210</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+6.37%</t>
+          <t>'+6.72%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.13</v>
       </c>
       <c r="E11" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="F11" t="n">
         <v>75</v>
       </c>
       <c r="G11" t="n">
-        <v>389</v>
+        <v>410</v>
       </c>
       <c r="H11" t="n">
         <v>5.47</v>
@@ -1438,7 +1438,7 @@
         <v>5.34</v>
       </c>
       <c r="O11" t="n">
-        <v>27312111435</v>
+        <v>28230527235</v>
       </c>
       <c r="P11" t="n">
         <v>14940</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>테슬라 관련주로 부각되며 9천원대 돌파 기대. 공매도 세력과의 움직임 주목.</t>
+          <t>명신산업, 테슬라 로보택시 상표 출원 및 9천원대 돌파 기대. 공매도 숏커버링 가능성과 함께 8800원 하향 이탈 없을 경우 9900원 돌파 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['테슬라', '공매도', '상표출원']</t>
+          <t>['테슬라', '상표출원', '숏커버링']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8710</v>
+        <v>8680</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+6.22%</t>
+          <t>'+5.85%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>75</v>
       </c>
       <c r="G12" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H12" t="n">
         <v>1.42</v>
@@ -1530,7 +1530,7 @@
         <v>1.15</v>
       </c>
       <c r="O12" t="n">
-        <v>126766587795</v>
+        <v>127397857195</v>
       </c>
       <c r="P12" t="n">
         <v>9820</v>
@@ -1579,21 +1579,21 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2562</v>
+        <v>2560</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+4.57%</t>
+          <t>'+4.49%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.68</v>
       </c>
       <c r="E13" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F13" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G13" t="n">
         <v>169</v>
@@ -1622,7 +1622,7 @@
         <v>1.01</v>
       </c>
       <c r="O13" t="n">
-        <v>90147398505</v>
+        <v>90716135561</v>
       </c>
       <c r="P13" t="n">
         <v>2965</v>
@@ -1682,13 +1682,13 @@
         <v>0.57</v>
       </c>
       <c r="E14" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G14" t="n">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="H14" t="n">
         <v>41.01</v>
@@ -1714,7 +1714,7 @@
         <v>40.44</v>
       </c>
       <c r="O14" t="n">
-        <v>241867979050</v>
+        <v>245486962850</v>
       </c>
       <c r="P14" t="n">
         <v>67300</v>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>178400</v>
+        <v>178700</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.35%</t>
+          <t>'+2.52%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1780,7 +1780,7 @@
         <v>394</v>
       </c>
       <c r="G15" t="n">
-        <v>2392</v>
+        <v>2363</v>
       </c>
       <c r="H15" t="n">
         <v>35.43</v>
@@ -1806,7 +1806,7 @@
         <v>35.49</v>
       </c>
       <c r="O15" t="n">
-        <v>186207001750</v>
+        <v>189759904300</v>
       </c>
       <c r="P15" t="n">
         <v>304000</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>지수 대비 부진한 주가 흐름 및 공매도 비율 증가. 네이버 주가 반등 의지 부족.</t>
+          <t>NAVER, 엔비디아 지분 투자에도 불구하고 주가 부진 및 외국인, 연기금 매도세. 공매도 비율 증가 및 지수 대비 낮은 상승률.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가흐름', '공매도', '소외주']</t>
+          <t>['지분투자', '매도세', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>29850</v>
+        <v>29800</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.19%</t>
+          <t>'+1.02%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F16" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G16" t="n">
-        <v>712</v>
+        <v>794</v>
       </c>
       <c r="H16" t="n">
         <v>28.81</v>
@@ -1892,13 +1892,13 @@
         <v>30650</v>
       </c>
       <c r="M16" t="n">
-        <v>29850</v>
+        <v>29800</v>
       </c>
       <c r="N16" t="n">
         <v>28.82</v>
       </c>
       <c r="O16" t="n">
-        <v>36122122525</v>
+        <v>37344477100</v>
       </c>
       <c r="P16" t="n">
         <v>69700</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>김범수 관련 이슈 지속되며 주가 약세. 전환사채 발행 및 유증 관련 의혹 제기.</t>
+          <t>카카오, 김범수 관련 의혹과 주가 조작 혐의로 인한 부정적 전망. 유증 및 전환사채 발행 관련 논란과 함께 거래량 부진.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['김범수', '전환사채', '주가약세']</t>
+          <t>['주가조작', '전환사채', '거래량']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1958,13 +1958,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F17" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G17" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H17" t="n">
         <v>28.03</v>
@@ -1990,7 +1990,7 @@
         <v>27.96</v>
       </c>
       <c r="O17" t="n">
-        <v>61888959535</v>
+        <v>63385643350</v>
       </c>
       <c r="P17" t="n">
         <v>35350</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52400</v>
+        <v>52500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-1.13%</t>
+          <t>'-0.94%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="F18" t="n">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="G18" t="n">
-        <v>1423</v>
+        <v>1451</v>
       </c>
       <c r="H18" t="n">
         <v>10.31</v>
@@ -2082,7 +2082,7 @@
         <v>10.34</v>
       </c>
       <c r="O18" t="n">
-        <v>86088607450</v>
+        <v>86569043050</v>
       </c>
       <c r="P18" t="n">
         <v>154800</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2분기 실적 호조에도 주가 하락 지속. 증권가 평가 및 미국 조선업 협력 난항 우려.</t>
+          <t>한화오션, 코스피 대세 상승에도 불구하고 주가 하락 및 실적 부진에 대한 우려. 15만원 및 10만원 위로 매물대 존재.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['실적', '주가하락', '조선업']</t>
+          <t>['실적', '대세상승', '매물대']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2142,13 +2142,13 @@
         <v>-0.19</v>
       </c>
       <c r="E19" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F19" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G19" t="n">
-        <v>698</v>
+        <v>710</v>
       </c>
       <c r="H19" t="n">
         <v>9.83</v>
@@ -2174,7 +2174,7 @@
         <v>10.02</v>
       </c>
       <c r="O19" t="n">
-        <v>67257958205</v>
+        <v>67907827275</v>
       </c>
       <c r="P19" t="n">
         <v>40350</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2040</v>
+        <v>2035</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-2.16%</t>
+          <t>'-2.40%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.39</v>
       </c>
       <c r="E20" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F20" t="n">
         <v>55</v>
       </c>
       <c r="G20" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H20" t="n">
         <v>2.52</v>
@@ -2266,7 +2266,7 @@
         <v>2.13</v>
       </c>
       <c r="O20" t="n">
-        <v>17170029244</v>
+        <v>17320338392</v>
       </c>
       <c r="P20" t="n">
         <v>6190</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2080</v>
+        <v>2095</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-4.15%</t>
+          <t>'-3.46%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.18</v>
       </c>
       <c r="E21" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F21" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G21" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H21" t="n">
         <v>5.07</v>
@@ -2358,7 +2358,7 @@
         <v>4.89</v>
       </c>
       <c r="O21" t="n">
-        <v>52619875485</v>
+        <v>53004310955</v>
       </c>
       <c r="P21" t="n">
         <v>4980</v>
@@ -2407,18 +2407,18 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9000</v>
+        <v>9040</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-5.56%</t>
+          <t>'-5.14%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.83</v>
       </c>
       <c r="E22" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F22" t="n">
         <v>56</v>
@@ -2450,7 +2450,7 @@
         <v>2.63</v>
       </c>
       <c r="O22" t="n">
-        <v>46989764455</v>
+        <v>47385011080</v>
       </c>
       <c r="P22" t="n">
         <v>11690</v>

--- a/data/trending_integrated_20261028_15.xlsx
+++ b/data/trending_integrated_20261028_15.xlsx
@@ -578,13 +578,13 @@
         <v>-0.19</v>
       </c>
       <c r="E2" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F2" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G2" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>151495479296</v>
+        <v>151536313426</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19130</v>
+        <v>19210</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.85%</t>
+          <t>'+21.35%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.02</v>
       </c>
       <c r="E3" t="n">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="F3" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G3" t="n">
-        <v>517</v>
+        <v>545</v>
       </c>
       <c r="H3" t="n">
         <v>1.11</v>
@@ -702,7 +702,7 @@
         <v>0.09</v>
       </c>
       <c r="O3" t="n">
-        <v>415208854275</v>
+        <v>416636483845</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 뉴스. 4분기 공급 가시화.</t>
+          <t>멜콘, 미국 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 소식에 따른 급등 기대. 전 세계 반도체 공급망 내 주요 역할 부각.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['반도체장비', '공급망', 'ASML']</t>
+          <t>['반도체 장비', '공급망', '마이크론']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,21 +751,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27950</v>
+        <v>28000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.68%</t>
+          <t>'+17.89%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F4" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
         <v>284</v>
@@ -794,7 +794,7 @@
         <v>5.31</v>
       </c>
       <c r="O4" t="n">
-        <v>180000014025</v>
+        <v>181275386025</v>
       </c>
       <c r="P4" t="n">
         <v>50600</v>
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1494000</v>
+        <v>190100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.41%</t>
+          <t>'+11.10%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>800</v>
+        <v>96</v>
       </c>
       <c r="F5" t="n">
-        <v>493</v>
+        <v>73</v>
       </c>
       <c r="G5" t="n">
-        <v>2000</v>
+        <v>478</v>
       </c>
       <c r="H5" t="n">
-        <v>48.61</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,91 +871,91 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1341000</v>
+        <v>171100</v>
       </c>
       <c r="K5" t="n">
-        <v>1390000</v>
+        <v>176300</v>
       </c>
       <c r="L5" t="n">
-        <v>1495000</v>
+        <v>190800</v>
       </c>
       <c r="M5" t="n">
-        <v>1358000</v>
+        <v>175400</v>
       </c>
       <c r="N5" t="n">
-        <v>48.66</v>
+        <v>74.89</v>
       </c>
       <c r="O5" t="n">
-        <v>5134076303500</v>
+        <v>821814848750</v>
       </c>
       <c r="P5" t="n">
-        <v>2987000</v>
+        <v>243500</v>
       </c>
       <c r="Q5" t="n">
-        <v>501000</v>
+        <v>71000</v>
       </c>
       <c r="R5" t="n">
-        <v>285000</v>
+        <v>1017000</v>
       </c>
       <c r="S5" t="n">
-        <v>211000</v>
+        <v>-28000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>SK하이닉스, 200만원 및 470만원 목표가 제시와 함께 외국인 매수세 유입 기대. 29년 목표가 320만원 전망.</t>
+          <t>우선주 소각 및 실적 발표에 대한 기대감과 외국인 수급 긍정적. 숏 스퀴즈 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['목표가', '외국인', '실적발표']</t>
+          <t>['우선주 소각', '실적 발표', '외국인 수급']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>190100</v>
+        <v>1487000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.10%</t>
+          <t>'+10.89%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>95</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>72</v>
+        <v>491</v>
       </c>
       <c r="G6" t="n">
-        <v>468</v>
+        <v>2085</v>
       </c>
       <c r="H6" t="n">
-        <v>74.90000000000001</v>
+        <v>48.61</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,60 +963,60 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>171100</v>
+        <v>1341000</v>
       </c>
       <c r="K6" t="n">
-        <v>176300</v>
+        <v>1390000</v>
       </c>
       <c r="L6" t="n">
-        <v>190800</v>
+        <v>1495000</v>
       </c>
       <c r="M6" t="n">
-        <v>175400</v>
+        <v>1358000</v>
       </c>
       <c r="N6" t="n">
-        <v>74.89</v>
+        <v>48.66</v>
       </c>
       <c r="O6" t="n">
-        <v>789192738250</v>
+        <v>5612954244500</v>
       </c>
       <c r="P6" t="n">
-        <v>243500</v>
+        <v>2987000</v>
       </c>
       <c r="Q6" t="n">
-        <v>71000</v>
+        <v>501000</v>
       </c>
       <c r="R6" t="n">
-        <v>1017000</v>
+        <v>285000</v>
       </c>
       <c r="S6" t="n">
-        <v>-28000</v>
+        <v>211000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>우선주 소각 및 실적 발표에 대한 기대감과 외국인 수급 긍정적. 숏 스퀴즈 가능성 언급.</t>
+          <t>SK하이닉스, 200만원대 및 150만 돌파 기대감 속 외국인 매수세 유입 가능성 언급. 자사주 취득 및 삼성전자와의 동반 상승 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['우선주 소각', '실적 발표', '외국인 수급']</t>
+          <t>['자사주', '외국인 매수', '동반 상승']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14960</v>
+        <v>14980</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.20%</t>
+          <t>'+9.34%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1044,7 +1044,7 @@
         <v>87</v>
       </c>
       <c r="G7" t="n">
-        <v>781</v>
+        <v>799</v>
       </c>
       <c r="H7" t="n">
         <v>2.87</v>
@@ -1070,7 +1070,7 @@
         <v>2.82</v>
       </c>
       <c r="O7" t="n">
-        <v>177120895735</v>
+        <v>177695738255</v>
       </c>
       <c r="P7" t="n">
         <v>31500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>대한광통신, AI 수요 증가 및 메타 유리기판, 해상광통신 케이블 등 신기술 기반 2만원 돌파 전망. 외인 프로그램 적극 매수 및 미국 수주 유지.</t>
+          <t>대한광통신, 국민연금의 지속적인 매수 및 AI 수요 증가 관련 긍정적 전망. 메타 유리기판, 해상광통신 케이블 관련 뉴스 및 코스닥 150 편입 예정.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['AI수요', '유리기판', '수주']</t>
+          <t>['AI 수요', '유리기판', '코스닥 150']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>242250</v>
+        <v>242000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+9.12%</t>
+          <t>'+9.01%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G8" t="n">
-        <v>1592</v>
+        <v>1629</v>
       </c>
       <c r="H8" t="n">
         <v>46.15</v>
@@ -1162,7 +1162,7 @@
         <v>46.1</v>
       </c>
       <c r="O8" t="n">
-        <v>3597711000000</v>
+        <v>4005751072000</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>삼성전자, 주주환원 110조 발표 및 3분기 순이익 115조 예상 속 폭등 기대감. 공매도 세력에 대한 경고 및 긍정적 추세 전망.</t>
+          <t>삼성전자, 주주환원 110조 발표 및 3분기 순이익 115조 예상에 대한 기대감이 형성. 자사주 소각 공시 및 실적 발표 관련 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주주환원', '순이익', '공매도']</t>
+          <t>['주주환원', '순이익', '자사주']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18390</v>
+        <v>19260</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+7.61%</t>
+          <t>'+7.66%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.61</v>
+        <v>0.46</v>
       </c>
       <c r="E9" t="n">
-        <v>148</v>
+        <v>101</v>
       </c>
       <c r="F9" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>432</v>
+        <v>123</v>
       </c>
       <c r="H9" t="n">
-        <v>4.74</v>
+        <v>4.25</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,91 +1239,91 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17090</v>
+        <v>17890</v>
       </c>
       <c r="K9" t="n">
-        <v>19270</v>
+        <v>18250</v>
       </c>
       <c r="L9" t="n">
-        <v>20450</v>
+        <v>20000</v>
       </c>
       <c r="M9" t="n">
-        <v>18070</v>
+        <v>17950</v>
       </c>
       <c r="N9" t="n">
-        <v>4.13</v>
+        <v>3.79</v>
       </c>
       <c r="O9" t="n">
-        <v>47357230065</v>
+        <v>72950339040</v>
       </c>
       <c r="P9" t="n">
-        <v>28600</v>
+        <v>22450</v>
       </c>
       <c r="Q9" t="n">
-        <v>11050</v>
+        <v>6320</v>
       </c>
       <c r="R9" t="n">
-        <v>-59000</v>
+        <v>-7000</v>
       </c>
       <c r="S9" t="n">
-        <v>58000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>나무가, 11월 6일 로봇 눈 공개 및 AI 데이터센터 방열 시스템 594억 공급 계약 체결. 휴머노이드 및 현대차 로봇 2만 5천대 도입 관련 긍정적 전망.</t>
+          <t>국내외 해킹 사고 연이은 발생, 양자보안 의무화 등 보안 섹터 상승 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['로봇', '공급계약', '휴머노이드']</t>
+          <t>['보안', '해킹', '양자보안']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>190510</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19250</v>
+        <v>18310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+7.60%</t>
+          <t>'+7.14%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F10" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="G10" t="n">
-        <v>123</v>
+        <v>431</v>
       </c>
       <c r="H10" t="n">
-        <v>4.25</v>
+        <v>4.74</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,139 +1331,139 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17890</v>
+        <v>17090</v>
       </c>
       <c r="K10" t="n">
-        <v>18250</v>
+        <v>19270</v>
       </c>
       <c r="L10" t="n">
-        <v>20000</v>
+        <v>20450</v>
       </c>
       <c r="M10" t="n">
-        <v>17950</v>
+        <v>18070</v>
       </c>
       <c r="N10" t="n">
-        <v>3.79</v>
+        <v>4.13</v>
       </c>
       <c r="O10" t="n">
-        <v>72698052300</v>
+        <v>47609779895</v>
       </c>
       <c r="P10" t="n">
-        <v>22450</v>
+        <v>28600</v>
       </c>
       <c r="Q10" t="n">
-        <v>6320</v>
+        <v>11050</v>
       </c>
       <c r="R10" t="n">
-        <v>-7000</v>
+        <v>-59000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>58000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>국내외 해킹 사고 연이은 발생, 양자보안 의무화 등 보안 섹터 상승 기대.</t>
+          <t>나무가, 로봇 관련 사업 및 AI 데이터센터 방열 시스템 공급 계약 소식에 따른 기대감. 미국 휴머노이드 로봇 시장 성장 수혜 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['보안', '해킹', '양자보안']</t>
+          <t>['로봇', 'AI 데이터센터', '방열 시스템']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>190510</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9210</v>
+        <v>8750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+6.72%</t>
+          <t>'+6.71%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.13</v>
+        <v>0.27</v>
       </c>
       <c r="E11" t="n">
-        <v>172</v>
+        <v>97</v>
       </c>
       <c r="F11" t="n">
         <v>75</v>
       </c>
       <c r="G11" t="n">
-        <v>410</v>
+        <v>110</v>
       </c>
       <c r="H11" t="n">
-        <v>5.47</v>
+        <v>1.42</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8630</v>
+        <v>8200</v>
       </c>
       <c r="K11" t="n">
-        <v>8660</v>
+        <v>8230</v>
       </c>
       <c r="L11" t="n">
-        <v>9410</v>
+        <v>9780</v>
       </c>
       <c r="M11" t="n">
-        <v>8410</v>
+        <v>8100</v>
       </c>
       <c r="N11" t="n">
-        <v>5.34</v>
+        <v>1.15</v>
       </c>
       <c r="O11" t="n">
-        <v>28230527235</v>
+        <v>127734670945</v>
       </c>
       <c r="P11" t="n">
-        <v>14940</v>
+        <v>9820</v>
       </c>
       <c r="Q11" t="n">
-        <v>5390</v>
+        <v>2965</v>
       </c>
       <c r="R11" t="n">
-        <v>1000</v>
+        <v>-57000</v>
       </c>
       <c r="S11" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>명신산업, 테슬라 로보택시 상표 출원 및 9천원대 돌파 기대. 공매도 숏커버링 가능성과 함께 8800원 하향 이탈 없을 경우 9900원 돌파 전망.</t>
+          <t>미국 양자/보안주 급등 및 국내 해킹 사고 관련, 보안 테마 상승 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['테슬라', '상표출원', '숏커버링']</t>
+          <t>['보안', '해킹', '테마']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,91 +1471,91 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8680</v>
+        <v>9190</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+5.85%</t>
+          <t>'+6.49%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="E12" t="n">
-        <v>97</v>
+        <v>176</v>
       </c>
       <c r="F12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G12" t="n">
-        <v>107</v>
+        <v>421</v>
       </c>
       <c r="H12" t="n">
-        <v>1.42</v>
+        <v>5.47</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>8200</v>
+        <v>8630</v>
       </c>
       <c r="K12" t="n">
-        <v>8230</v>
+        <v>8660</v>
       </c>
       <c r="L12" t="n">
-        <v>9780</v>
+        <v>9410</v>
       </c>
       <c r="M12" t="n">
-        <v>8100</v>
+        <v>8410</v>
       </c>
       <c r="N12" t="n">
-        <v>1.15</v>
+        <v>5.34</v>
       </c>
       <c r="O12" t="n">
-        <v>127397857195</v>
+        <v>28582200965</v>
       </c>
       <c r="P12" t="n">
-        <v>9820</v>
+        <v>14940</v>
       </c>
       <c r="Q12" t="n">
-        <v>2965</v>
+        <v>5390</v>
       </c>
       <c r="R12" t="n">
-        <v>-57000</v>
+        <v>1000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 양자/보안주 급등 및 국내 해킹 사고 관련, 보안 테마 상승 기대.</t>
+          <t>명신산업, 테슬라 관련 긍정적 뉴스에 따른 주가 상승 기대감. 공매도 세력과의 대립 및 숏 커버링 가능성 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['보안', '해킹', '테마']</t>
+          <t>['테슬라', '공매도', '숏 커버링']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2560</v>
+        <v>2570</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+4.49%</t>
+          <t>'+4.90%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.68</v>
       </c>
       <c r="E13" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F13" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G13" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="H13" t="n">
         <v>1.69</v>
@@ -1622,7 +1622,7 @@
         <v>1.01</v>
       </c>
       <c r="O13" t="n">
-        <v>90716135561</v>
+        <v>91038488091</v>
       </c>
       <c r="P13" t="n">
         <v>2965</v>
@@ -1682,13 +1682,13 @@
         <v>0.57</v>
       </c>
       <c r="E14" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F14" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G14" t="n">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="H14" t="n">
         <v>41.01</v>
@@ -1714,7 +1714,7 @@
         <v>40.44</v>
       </c>
       <c r="O14" t="n">
-        <v>245486962850</v>
+        <v>253219082450</v>
       </c>
       <c r="P14" t="n">
         <v>67300</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>최근 4일간 코스피 수익률 1위 달성 및 자사주 매입 지속. 공매도 세력에 대한 경계.</t>
+          <t>삼성E&amp;A, 코스피 수익률 1위 달성 및 공매도 세력에 대한 경계감. 자사주 매입 지속 및 귀족주 진입 기대감.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['자사주 매입', '수익률', '공매도']</t>
+          <t>['코스피 수익률', '공매도', '자사주 매입']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>178700</v>
+        <v>178000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.52%</t>
+          <t>'+2.12%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="G15" t="n">
-        <v>2363</v>
+        <v>2423</v>
       </c>
       <c r="H15" t="n">
         <v>35.43</v>
@@ -1806,7 +1806,7 @@
         <v>35.49</v>
       </c>
       <c r="O15" t="n">
-        <v>189759904300</v>
+        <v>197382932300</v>
       </c>
       <c r="P15" t="n">
         <v>304000</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>NAVER, 엔비디아 지분 투자에도 불구하고 주가 부진 및 외국인, 연기금 매도세. 공매도 비율 증가 및 지수 대비 낮은 상승률.</t>
+          <t>NAVER, 주가 부진 및 기관/외인 매도에 대한 불만 표출. 엔비디아 지분 투자 및 대표 연봉 관련 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['지분투자', '매도세', '공매도']</t>
+          <t>['주가 부진', '기관 매도', '외인 매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1866,13 +1866,13 @@
         <v>-0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="F16" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G16" t="n">
-        <v>794</v>
+        <v>811</v>
       </c>
       <c r="H16" t="n">
         <v>28.81</v>
@@ -1898,7 +1898,7 @@
         <v>28.82</v>
       </c>
       <c r="O16" t="n">
-        <v>37344477100</v>
+        <v>39483103900</v>
       </c>
       <c r="P16" t="n">
         <v>69700</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16490</v>
+        <v>16510</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.61%</t>
+          <t>'+0.73%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F17" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G17" t="n">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="H17" t="n">
         <v>28.03</v>
@@ -1990,7 +1990,7 @@
         <v>27.96</v>
       </c>
       <c r="O17" t="n">
-        <v>63385643350</v>
+        <v>67232027580</v>
       </c>
       <c r="P17" t="n">
         <v>35350</v>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주문량 대비 주가 부진 지속. 애널리스트 보고서 및 실적 발표에 대한 불신.</t>
+          <t>삼성중공업, 수주 물량 대비 주가 부진에 대한 불만과 실적 발표 관련 불확실성 언급. 방산 독자 설계 능력 향상 가능성.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2050,13 +2050,13 @@
         <v>-0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F18" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G18" t="n">
-        <v>1451</v>
+        <v>1456</v>
       </c>
       <c r="H18" t="n">
         <v>10.31</v>
@@ -2082,7 +2082,7 @@
         <v>10.34</v>
       </c>
       <c r="O18" t="n">
-        <v>86569043050</v>
+        <v>90708878050</v>
       </c>
       <c r="P18" t="n">
         <v>154800</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14280</v>
+        <v>14270</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-1.18%</t>
+          <t>'-1.25%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.19</v>
       </c>
       <c r="E19" t="n">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="F19" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G19" t="n">
-        <v>710</v>
+        <v>727</v>
       </c>
       <c r="H19" t="n">
         <v>9.83</v>
@@ -2174,7 +2174,7 @@
         <v>10.02</v>
       </c>
       <c r="O19" t="n">
-        <v>67907827275</v>
+        <v>68594285625</v>
       </c>
       <c r="P19" t="n">
         <v>40350</v>
@@ -2223,18 +2223,18 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2035</v>
+        <v>2040</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-2.40%</t>
+          <t>'-2.16%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.39</v>
       </c>
       <c r="E20" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F20" t="n">
         <v>55</v>
@@ -2266,7 +2266,7 @@
         <v>2.13</v>
       </c>
       <c r="O20" t="n">
-        <v>17320338392</v>
+        <v>17408537792</v>
       </c>
       <c r="P20" t="n">
         <v>6190</v>
@@ -2315,18 +2315,18 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2095</v>
+        <v>2100</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-3.46%</t>
+          <t>'-3.23%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.18</v>
       </c>
       <c r="E21" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F21" t="n">
         <v>50</v>
@@ -2358,7 +2358,7 @@
         <v>4.89</v>
       </c>
       <c r="O21" t="n">
-        <v>53004310955</v>
+        <v>53155975055</v>
       </c>
       <c r="P21" t="n">
         <v>4980</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9040</v>
+        <v>9000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-5.14%</t>
+          <t>'-5.56%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.83</v>
       </c>
       <c r="E22" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F22" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G22" t="n">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="H22" t="n">
         <v>3.46</v>
@@ -2450,7 +2450,7 @@
         <v>2.63</v>
       </c>
       <c r="O22" t="n">
-        <v>47385011080</v>
+        <v>47744318080</v>
       </c>
       <c r="P22" t="n">
         <v>11690</v>

--- a/data/trending_integrated_20261028_15.xlsx
+++ b/data/trending_integrated_20261028_15.xlsx
@@ -578,13 +578,13 @@
         <v>-0.19</v>
       </c>
       <c r="E2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F2" t="n">
         <v>89</v>
       </c>
       <c r="G2" t="n">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>151536313426</v>
+        <v>151542266131</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 광통신주 상승에 따른 기대감. 상한가 기록 및 연상 기대.</t>
+          <t>빛과전자, 연이은 상한가 기록 및 전고점 돌파 시도. 광통신 섹터 훈풍에 대한 기대감 반영.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광통신', '상한가', '연상']</t>
+          <t>['연상', '전고점', '광통신']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>1.02</v>
       </c>
       <c r="E3" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F3" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G3" t="n">
-        <v>545</v>
+        <v>555</v>
       </c>
       <c r="H3" t="n">
         <v>1.11</v>
@@ -702,7 +702,7 @@
         <v>0.09</v>
       </c>
       <c r="O3" t="n">
-        <v>416636483845</v>
+        <v>416756680815</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>멜콘, 미국 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 소식에 따른 급등 기대. 전 세계 반도체 공급망 내 주요 역할 부각.</t>
+          <t>멜콘, 마이크론 장비 평가 완료 및 ASML 공급망 진입 뉴스 부각. 반도체 섹터 내 주가 상승 기대감 고조.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['반도체 장비', '공급망', '마이크론']</t>
+          <t>['마이크론', 'ASML', '공급망']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,7 +762,7 @@
         <v>-0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F4" t="n">
         <v>51</v>
@@ -794,7 +794,7 @@
         <v>5.31</v>
       </c>
       <c r="O4" t="n">
-        <v>181275386025</v>
+        <v>181319458025</v>
       </c>
       <c r="P4" t="n">
         <v>50600</v>
@@ -854,13 +854,13 @@
         <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G5" t="n">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="H5" t="n">
         <v>74.90000000000001</v>
@@ -886,7 +886,7 @@
         <v>74.89</v>
       </c>
       <c r="O5" t="n">
-        <v>821814848750</v>
+        <v>822206834950</v>
       </c>
       <c r="P5" t="n">
         <v>243500</v>
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="G6" t="n">
-        <v>2085</v>
+        <v>2112</v>
       </c>
       <c r="H6" t="n">
         <v>48.61</v>
@@ -978,7 +978,7 @@
         <v>48.66</v>
       </c>
       <c r="O6" t="n">
-        <v>5612954244500</v>
+        <v>5613187703500</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>SK하이닉스, 200만원대 및 150만 돌파 기대감 속 외국인 매수세 유입 가능성 언급. 자사주 취득 및 삼성전자와의 동반 상승 기대.</t>
+          <t>SK하이닉스, 자사주 취득 발표 및 20일선 돌파로 상승 기대감 증폭. AI 관련 긍정적 전망 부각.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['자사주', '외국인 매수', '동반 상승']</t>
+          <t>['자사주 취득', '20일선 돌파', 'AI']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1038,13 +1038,13 @@
         <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F7" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G7" t="n">
-        <v>799</v>
+        <v>822</v>
       </c>
       <c r="H7" t="n">
         <v>2.87</v>
@@ -1070,7 +1070,7 @@
         <v>2.82</v>
       </c>
       <c r="O7" t="n">
-        <v>177695738255</v>
+        <v>177720350395</v>
       </c>
       <c r="P7" t="n">
         <v>31500</v>
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="G8" t="n">
-        <v>1629</v>
+        <v>1662</v>
       </c>
       <c r="H8" t="n">
         <v>46.15</v>
@@ -1162,7 +1162,7 @@
         <v>46.1</v>
       </c>
       <c r="O8" t="n">
-        <v>4005751072000</v>
+        <v>4005912486000</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>삼성전자, 주주환원 110조 발표 및 3분기 순이익 115조 예상에 대한 기대감이 형성. 자사주 소각 공시 및 실적 발표 관련 언급.</t>
+          <t>삼성전자, 증권사 목표주가 상향 및 실적 발표 기대감으로 매수세 유입 전망. 자체 주주환원 110조 발표 가능성 제기.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주주환원', '순이익', '자사주']</t>
+          <t>['목표주가', '실적 발표', '주주환원']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1228,7 +1228,7 @@
         <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H9" t="n">
         <v>4.25</v>
@@ -1254,7 +1254,7 @@
         <v>3.79</v>
       </c>
       <c r="O9" t="n">
-        <v>72950339040</v>
+        <v>72955192560</v>
       </c>
       <c r="P9" t="n">
         <v>22450</v>
@@ -1314,13 +1314,13 @@
         <v>0.61</v>
       </c>
       <c r="E10" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F10" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G10" t="n">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="H10" t="n">
         <v>4.74</v>
@@ -1346,7 +1346,7 @@
         <v>4.13</v>
       </c>
       <c r="O10" t="n">
-        <v>47609779895</v>
+        <v>47609798205</v>
       </c>
       <c r="P10" t="n">
         <v>28600</v>
@@ -1438,7 +1438,7 @@
         <v>1.15</v>
       </c>
       <c r="O11" t="n">
-        <v>127734670945</v>
+        <v>127799884695</v>
       </c>
       <c r="P11" t="n">
         <v>9820</v>
@@ -1504,7 +1504,7 @@
         <v>78</v>
       </c>
       <c r="G12" t="n">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="H12" t="n">
         <v>5.47</v>
@@ -1530,7 +1530,7 @@
         <v>5.34</v>
       </c>
       <c r="O12" t="n">
-        <v>28582200965</v>
+        <v>28582485855</v>
       </c>
       <c r="P12" t="n">
         <v>14940</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>명신산업, 테슬라 관련 긍정적 뉴스에 따른 주가 상승 기대감. 공매도 세력과의 대립 및 숏 커버링 가능성 언급.</t>
+          <t>명신산업, 테슬라 관련 호재 및 공매도 숏커버링 기대감으로 주가 상승 전망. 상표 출원 사실 확인.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['테슬라', '공매도', '숏 커버링']</t>
+          <t>['테슬라', '공매도', '숏커버링']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1590,13 +1590,13 @@
         <v>0.68</v>
       </c>
       <c r="E13" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F13" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G13" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H13" t="n">
         <v>1.69</v>
@@ -1622,7 +1622,7 @@
         <v>1.01</v>
       </c>
       <c r="O13" t="n">
-        <v>91038488091</v>
+        <v>91040477271</v>
       </c>
       <c r="P13" t="n">
         <v>2965</v>
@@ -1682,13 +1682,13 @@
         <v>0.57</v>
       </c>
       <c r="E14" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="F14" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G14" t="n">
-        <v>868</v>
+        <v>887</v>
       </c>
       <c r="H14" t="n">
         <v>41.01</v>
@@ -1714,7 +1714,7 @@
         <v>40.44</v>
       </c>
       <c r="O14" t="n">
-        <v>253219082450</v>
+        <v>253254007250</v>
       </c>
       <c r="P14" t="n">
         <v>67300</v>
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G15" t="n">
-        <v>2423</v>
+        <v>2462</v>
       </c>
       <c r="H15" t="n">
         <v>35.43</v>
@@ -1806,7 +1806,7 @@
         <v>35.49</v>
       </c>
       <c r="O15" t="n">
-        <v>197382932300</v>
+        <v>197392188300</v>
       </c>
       <c r="P15" t="n">
         <v>304000</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>NAVER, 주가 부진 및 기관/외인 매도에 대한 불만 표출. 엔비디아 지분 투자 및 대표 연봉 관련 언급.</t>
+          <t>NAVER, 타 종목 대비 주가 부진 및 외국인/연기금 매도세 지속. 공매도 비율 높은 가운데 상승 동력 부재.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가 부진', '기관 매도', '외인 매도']</t>
+          <t>['주가 부진', '공매도', '매도세']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1866,13 +1866,13 @@
         <v>-0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="F16" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G16" t="n">
-        <v>811</v>
+        <v>869</v>
       </c>
       <c r="H16" t="n">
         <v>28.81</v>
@@ -1898,7 +1898,7 @@
         <v>28.82</v>
       </c>
       <c r="O16" t="n">
-        <v>39483103900</v>
+        <v>39489302300</v>
       </c>
       <c r="P16" t="n">
         <v>69700</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>카카오, 김범수 관련 의혹과 주가 조작 혐의로 인한 부정적 전망. 유증 및 전환사채 발행 관련 논란과 함께 거래량 부진.</t>
+          <t>카카오, 경영진 무능 비판 및 유증/스톡옵션 발행에 대한 부정적 시각. 타사 대비 주가 흐름 답보.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주가조작', '전환사채', '거래량']</t>
+          <t>['경영진', '유증', '스톡옵션']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1958,13 +1958,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F17" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G17" t="n">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="H17" t="n">
         <v>28.03</v>
@@ -1990,7 +1990,7 @@
         <v>27.96</v>
       </c>
       <c r="O17" t="n">
-        <v>67232027580</v>
+        <v>67234338980</v>
       </c>
       <c r="P17" t="n">
         <v>35350</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>삼성중공업, 수주 물량 대비 주가 부진에 대한 불만과 실적 발표 관련 불확실성 언급. 방산 독자 설계 능력 향상 가능성.</t>
+          <t>삼성중공업, 수주 물량 대비 주가 부진 지속. 애널리스트 보고서 및 실적 발표에 대한 불신감 형성.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['수주', '실적 발표', '주가 부진']</t>
+          <t>['수주 물량', '주가 부진', '실적 발표']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2050,13 +2050,13 @@
         <v>-0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="F18" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G18" t="n">
-        <v>1456</v>
+        <v>1463</v>
       </c>
       <c r="H18" t="n">
         <v>10.31</v>
@@ -2082,7 +2082,7 @@
         <v>10.34</v>
       </c>
       <c r="O18" t="n">
-        <v>90708878050</v>
+        <v>90710085550</v>
       </c>
       <c r="P18" t="n">
         <v>154800</v>
@@ -2142,13 +2142,13 @@
         <v>-0.19</v>
       </c>
       <c r="E19" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F19" t="n">
         <v>128</v>
       </c>
       <c r="G19" t="n">
-        <v>727</v>
+        <v>761</v>
       </c>
       <c r="H19" t="n">
         <v>9.83</v>
@@ -2174,7 +2174,7 @@
         <v>10.02</v>
       </c>
       <c r="O19" t="n">
-        <v>68594285625</v>
+        <v>68615362415</v>
       </c>
       <c r="P19" t="n">
         <v>40350</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>코스피 지수 상승에도 불구하고 주가 하락 및 경영진에 대한 불만 표출. 답답한 주가 흐름.</t>
+          <t>대우건설, 영업이익 상승에도 주가 하락 및 코스피 지수 상승장에서 소외. 경영진에 대한 불만 고조.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2234,13 +2234,13 @@
         <v>0.39</v>
       </c>
       <c r="E20" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F20" t="n">
         <v>55</v>
       </c>
       <c r="G20" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="H20" t="n">
         <v>2.52</v>
@@ -2266,7 +2266,7 @@
         <v>2.13</v>
       </c>
       <c r="O20" t="n">
-        <v>17408537792</v>
+        <v>17411259152</v>
       </c>
       <c r="P20" t="n">
         <v>6190</v>
@@ -2326,13 +2326,13 @@
         <v>0.18</v>
       </c>
       <c r="E21" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F21" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G21" t="n">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="H21" t="n">
         <v>5.07</v>
@@ -2358,7 +2358,7 @@
         <v>4.89</v>
       </c>
       <c r="O21" t="n">
-        <v>53155975055</v>
+        <v>53173909055</v>
       </c>
       <c r="P21" t="n">
         <v>4980</v>
@@ -2418,13 +2418,13 @@
         <v>0.83</v>
       </c>
       <c r="E22" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F22" t="n">
         <v>59</v>
       </c>
       <c r="G22" t="n">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="H22" t="n">
         <v>3.46</v>
@@ -2450,7 +2450,7 @@
         <v>2.63</v>
       </c>
       <c r="O22" t="n">
-        <v>47744318080</v>
+        <v>47764685080</v>
       </c>
       <c r="P22" t="n">
         <v>11690</v>
